--- a/config/journal2.xlsx
+++ b/config/journal2.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="35" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{52FC03B6-A56A-449D-8E68-7333BB45A8F9}"/>
+  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB09F75-DD63-4D68-BF32-08A246680B21}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="1" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
   <sheets>
     <sheet name="readme" sheetId="2" r:id="rId1"/>
@@ -1385,6 +1385,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2387,7 +2391,7 @@
         <v>102</v>
       </c>
       <c r="F6" s="11">
-        <v>0</v>
+        <v>7.1999999999999999E-7</v>
       </c>
       <c r="G6" s="29" t="s">
         <v>103</v>
@@ -2456,7 +2460,7 @@
         <v>102</v>
       </c>
       <c r="F9" s="11">
-        <v>0</v>
+        <v>7.1999999999999999E-7</v>
       </c>
       <c r="G9" s="29" t="s">
         <v>103</v>
@@ -3068,7 +3072,7 @@
         <v>48</v>
       </c>
       <c r="F18" s="9">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G18" s="31" t="s">
         <v>16</v>

--- a/config/journal2.xlsx
+++ b/config/journal2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="46" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ADB09F75-DD63-4D68-BF32-08A246680B21}"/>
+  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77ABD45-8693-4B95-A28D-B3EDB9CE03FE}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>

--- a/config/journal2.xlsx
+++ b/config/journal2.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f215465b21b5e6e2/Studium/34_Github/TherMOS/config/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\schir\OneDrive\Studium\34_Github\TherMOS\config\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="48" documentId="13_ncr:1_{7354D1B3-3AA5-43CF-A80E-70316BF1D728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A77ABD45-8693-4B95-A28D-B3EDB9CE03FE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FEB1A52-2622-439F-AE99-9EACE7B3D19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="16896" activeTab="3" xr2:uid="{DB7D2548-4471-4992-93B1-3EC0BA66F7EA}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="448" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="508" uniqueCount="260">
   <si>
     <t>#</t>
   </si>
@@ -798,6 +798,91 @@
   </si>
   <si>
     <t>Emax</t>
+  </si>
+  <si>
+    <t>BasisFunction</t>
+  </si>
+  <si>
+    <t>gpr</t>
+  </si>
+  <si>
+    <t>Explicit basis in the GPR model:
+1) Constant
+2) Linear
+3) Quadratic</t>
+  </si>
+  <si>
+    <t>basis</t>
+  </si>
+  <si>
+    <t>Form of the covariance function, specified as one of the following:
+1) Exponential
+2) Squareexponential</t>
+  </si>
+  <si>
+    <t>IterationLimit</t>
+  </si>
+  <si>
+    <t>Maximum number of block coordinate descent method ("bcd") iterations.</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>en</t>
+  </si>
+  <si>
+    <t>Ensemble aggregation method:
+1) LSBoost
+2) Bag</t>
+  </si>
+  <si>
+    <t>method</t>
+  </si>
+  <si>
+    <t>LearningCycles</t>
+  </si>
+  <si>
+    <t>Number of ensemble learning cycles</t>
+  </si>
+  <si>
+    <t>cycle</t>
+  </si>
+  <si>
+    <t>nn</t>
+  </si>
+  <si>
+    <t>Maximum number of training iterations</t>
+  </si>
+  <si>
+    <t>NumberLayers</t>
+  </si>
+  <si>
+    <t>Number of fully connected layers in the network.</t>
+  </si>
+  <si>
+    <t>layer</t>
+  </si>
+  <si>
+    <t>NumberNeurons</t>
+  </si>
+  <si>
+    <t>Number of nodes per fully connected layer.</t>
+  </si>
+  <si>
+    <t>nodes</t>
+  </si>
+  <si>
+    <t>Activation</t>
+  </si>
+  <si>
+    <t>Activation functions for the fully connected layers of the neural network model:
+1) relu
+2) tanh
+3) sigmoid</t>
+  </si>
+  <si>
+    <t>act</t>
   </si>
 </sst>
 </file>
@@ -1385,10 +1470,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2654,7 +2735,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{799FBFCB-8244-4B83-8CC9-EBD2890613E5}">
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G53"/>
   <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="29.33203125" bestFit="1" customWidth="1"/>
@@ -3559,54 +3640,284 @@
         <v>16</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="12"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="8"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="9"/>
-      <c r="G40" s="31"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="13"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="5"/>
-      <c r="D41" s="26"/>
-      <c r="E41" s="26"/>
-      <c r="F41" s="6"/>
-      <c r="G41" s="29"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A42" s="13"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="5"/>
-      <c r="D42" s="26"/>
-      <c r="E42" s="26"/>
-      <c r="F42" s="6"/>
-      <c r="G42" s="29"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="13"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="5"/>
-      <c r="D43" s="26"/>
-      <c r="E43" s="26"/>
-      <c r="F43" s="6"/>
-      <c r="G43" s="29"/>
+    <row r="40" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="B40" s="28" t="s">
+        <v>236</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="D40" s="28" t="s">
+        <v>238</v>
+      </c>
+      <c r="E40" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F40" s="48">
+        <v>1</v>
+      </c>
+      <c r="G40" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>192</v>
+      </c>
+      <c r="B41" s="26" t="s">
+        <v>236</v>
+      </c>
+      <c r="C41" s="5" t="s">
+        <v>239</v>
+      </c>
+      <c r="D41" s="26" t="s">
+        <v>199</v>
+      </c>
+      <c r="E41" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F41" s="6">
+        <v>1</v>
+      </c>
+      <c r="G41" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" ht="29.4" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A42" s="14" t="s">
+        <v>240</v>
+      </c>
+      <c r="B42" s="27" t="s">
+        <v>236</v>
+      </c>
+      <c r="C42" s="7" t="s">
+        <v>241</v>
+      </c>
+      <c r="D42" s="27" t="s">
+        <v>158</v>
+      </c>
+      <c r="E42" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F42" s="10">
+        <v>100</v>
+      </c>
+      <c r="G42" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B43" s="28" t="s">
+        <v>243</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="D43" s="28" t="s">
+        <v>245</v>
+      </c>
+      <c r="E43" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F43" s="9">
+        <v>1</v>
+      </c>
+      <c r="G43" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>246</v>
+      </c>
+      <c r="B44" s="26" t="s">
+        <v>243</v>
+      </c>
+      <c r="C44" s="5" t="s">
+        <v>247</v>
+      </c>
+      <c r="D44" s="26" t="s">
+        <v>248</v>
+      </c>
+      <c r="E44" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F44" s="6">
+        <v>100</v>
+      </c>
+      <c r="G44" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" ht="58.2" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="14" t="s">
+        <v>179</v>
+      </c>
+      <c r="B45" s="27" t="s">
+        <v>243</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="D45" s="27" t="s">
+        <v>182</v>
+      </c>
+      <c r="E45" s="27" t="s">
+        <v>107</v>
+      </c>
+      <c r="F45" s="10">
+        <v>50</v>
+      </c>
+      <c r="G45" s="30" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B46" s="28" t="s">
+        <v>249</v>
+      </c>
+      <c r="C46" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="D46" s="28" t="s">
+        <v>158</v>
+      </c>
+      <c r="E46" s="28" t="s">
+        <v>107</v>
+      </c>
+      <c r="F46" s="9">
+        <v>100</v>
+      </c>
+      <c r="G46" s="31" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A47" s="13" t="s">
+        <v>251</v>
+      </c>
+      <c r="B47" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C47" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="D47" s="26" t="s">
+        <v>253</v>
+      </c>
+      <c r="E47" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F47" s="6">
+        <v>1</v>
+      </c>
+      <c r="G47" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A48" s="13" t="s">
+        <v>254</v>
+      </c>
+      <c r="B48" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C48" s="5" t="s">
+        <v>255</v>
+      </c>
+      <c r="D48" s="26" t="s">
+        <v>256</v>
+      </c>
+      <c r="E48" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="6">
+        <v>50</v>
+      </c>
+      <c r="G48" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" ht="72" x14ac:dyDescent="0.3">
+      <c r="A49" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B49" s="26" t="s">
+        <v>249</v>
+      </c>
+      <c r="C49" s="5" t="s">
+        <v>258</v>
+      </c>
+      <c r="D49" s="26" t="s">
+        <v>259</v>
+      </c>
+      <c r="E49" s="26" t="s">
+        <v>107</v>
+      </c>
+      <c r="F49" s="9">
+        <v>1</v>
+      </c>
+      <c r="G49" s="29" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A50" s="13"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="26"/>
+      <c r="E50" s="26"/>
+      <c r="F50" s="6"/>
+      <c r="G50" s="29"/>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A51" s="13"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="5"/>
+      <c r="D51" s="26"/>
+      <c r="E51" s="26"/>
+      <c r="F51" s="6"/>
+      <c r="G51" s="29"/>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A52" s="13"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="26"/>
+      <c r="F52" s="6"/>
+      <c r="G52" s="29"/>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A53" s="13"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="26"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="29"/>
     </row>
   </sheetData>
   <dataValidations count="12">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F40:F43" xr:uid="{257EC82B-68B5-4F35-825F-C289285A7C45}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F50:F53" xr:uid="{FDF4B16A-AED2-4AD7-916F-7B325F0A43EC}">
       <formula1>"fs, fel"</formula1>
     </dataValidation>
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F12 F10 F18 F20 F25 F23 F38" xr:uid="{3798FD8E-D43D-4D9F-BE2C-52321394B345}">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F13:F17 F21 F41 F43" xr:uid="{71E12662-7031-4247-910F-BB7CE1CF6CD0}">
       <formula1>"1, 2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F19 F26 F36 F40 F49 F47" xr:uid="{37FEDC31-329E-44E8-806D-0ED1512CF102}">
       <formula1>"1, 2, 3"</formula1>
     </dataValidation>
     <dataValidation type="whole" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F8" xr:uid="{42D8AC35-50A5-40BC-BBFA-BE08B273A500}">
@@ -3630,7 +3941,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F22" xr:uid="{47B450A3-D6D0-4908-B7DA-713464E39E93}">
       <formula1>"1, 2, 3, 4"</formula1>
     </dataValidation>
-    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
+    <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F24 F29 F32 F34:F35 F37 F39 F44:F46 F42 F48" xr:uid="{4036D9AA-DD26-43F2-86CA-83C98477498F}">
       <formula1>1</formula1>
     </dataValidation>
     <dataValidation type="decimal" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F27:F28 F30:F31 F33" xr:uid="{E87A8820-6156-4E10-8AF9-95041973A5CF}">
